--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2819</v>
+        <v>2821</v>
       </c>
       <c r="Q2" t="n">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="R2" t="n">
-        <v>3700</v>
+        <v>3705</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,39 +653,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바론짐 PT &amp; 필라테스 선유도점</t>
+          <t>짐베스트 당산생각공장점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>barongym@naver.com</t>
+          <t>gymbest2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1441-4014</t>
+          <t>0507-1449-4666</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 양평로 127 6층</t>
+          <t>서울특별시 영등포구 영등포로 150 생각공장 당산 C동 지하1층 엘113, 122호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://litt.ly/barongym2</t>
+          <t>https://blog.naver.com/gymbest2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>120</v>
+        <v>967</v>
       </c>
       <c r="Q3" t="n">
-        <v>1283</v>
+        <v>1261</v>
       </c>
       <c r="R3" t="n">
-        <v>1403</v>
+        <v>2228</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2019478029</t>
+          <t>2066500608</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019478029</t>
+          <t>https://m.place.naver.com/place/2066500608</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더라인핏 PT&amp;필라테스 신길점</t>
+          <t>바론짐 PT &amp; 필라테스 선유도점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thelinefitpt@naver.com</t>
+          <t>barongym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1427-4181</t>
+          <t>0507-1441-4014</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
+          <t>서울특별시 영등포구 양평로 127 6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thelinefitpt</t>
+          <t>https://litt.ly/barongym2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="Q4" t="n">
-        <v>879</v>
+        <v>1297</v>
       </c>
       <c r="R4" t="n">
-        <v>1007</v>
+        <v>1417</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1186860079</t>
+          <t>2019478029</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186860079</t>
+          <t>https://m.place.naver.com/place/2019478029</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT리프 당산점</t>
+          <t>더라인핏 PT&amp;필라테스 신길점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pt_studio_leaf@naver.com</t>
+          <t>thelinefitpt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1418-8235</t>
+          <t>0507-1427-4181</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 당산로 233 5층</t>
+          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pt_studio_leaf</t>
+          <t>https://blog.naver.com/thelinefitpt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="Q5" t="n">
-        <v>327</v>
+        <v>885</v>
       </c>
       <c r="R5" t="n">
-        <v>362</v>
+        <v>1013</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2042258974</t>
+          <t>1186860079</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042258974</t>
+          <t>https://m.place.naver.com/place/1186860079</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바디채널 바레톤 여의도점</t>
+          <t>PT리프 당산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bodych16@naver.com</t>
+          <t>pt_studio_leaf@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1367-5553</t>
+          <t>0507-1418-8235</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의대방로65길 24 호성빌딩 3, 4층 바디채널 바레톤 여의도점</t>
+          <t>서울특별시 영등포구 당산로 233 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.bodychannel.co.kr</t>
+          <t>https://blog.naver.com/pt_studio_leaf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>371</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>1292</v>
+        <v>326</v>
       </c>
       <c r="R6" t="n">
-        <v>1663</v>
+        <v>361</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1640622698</t>
+          <t>2042258974</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1640622698</t>
+          <t>https://m.place.naver.com/place/2042258974</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>베르데미 PT+필라테스 보라매점</t>
+          <t>바디채널 바레톤 여의도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verdemy@naver.com</t>
+          <t>bodych16@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-1665</t>
+          <t>0507-1367-5553</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의대방로 105 3층</t>
+          <t>서울특별시 영등포구 여의대방로65길 24 호성빌딩 3, 4층 바디채널 바레톤 여의도점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/verdemy</t>
+          <t>https://www.bodychannel.co.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="Q7" t="n">
-        <v>612</v>
+        <v>1292</v>
       </c>
       <c r="R7" t="n">
-        <v>956</v>
+        <v>1664</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1877385448</t>
+          <t>1640622698</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877385448</t>
+          <t>https://m.place.naver.com/place/1640622698</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 롯데마트 양평점</t>
+          <t>바르다짐 PT&amp;헬스 신길동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy00092@naver.com</t>
+          <t>generaltrainer@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-5125</t>
+          <t>0507-1463-1434</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 선유로 138 2층</t>
+          <t>서울특별시 영등포구 가마산로89길 5 2, 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy00092</t>
+          <t>https://www.instagram.com/barda_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>268</v>
       </c>
       <c r="R8" t="n">
-        <v>117</v>
+        <v>464</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2082705376</t>
+          <t>1684620094</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082705376</t>
+          <t>https://m.place.naver.com/place/1684620094</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1311,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아메리카요가 여의도점</t>
+          <t>테리온휘트니스 당산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ayo-yeouido@naver.com</t>
+          <t>cieleun1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1415-4549</t>
+          <t>0507-1371-9006</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
+          <t>서울특별시 영등포구 영신로 238 6,7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ayo-yeouido</t>
+          <t>https://www.instagram.com/terionfit/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>312</v>
+        <v>864</v>
       </c>
       <c r="Q10" t="n">
-        <v>1192</v>
+        <v>1084</v>
       </c>
       <c r="R10" t="n">
-        <v>1504</v>
+        <v>1948</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>12977695</t>
+          <t>1234987622</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12977695</t>
+          <t>https://m.place.naver.com/place/1234987622</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>벤골프앤피트니스 여의도본점</t>
+          <t>아메리카요가 여의도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bengolf81@naver.com</t>
+          <t>ayo-yeouido@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1432-7870</t>
+          <t>0507-1415-4549</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
+          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengolf_fitness</t>
+          <t>https://blog.naver.com/ayo-yeouido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="Q11" t="n">
-        <v>138</v>
+        <v>1192</v>
       </c>
       <c r="R11" t="n">
-        <v>327</v>
+        <v>1504</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,109 +1482,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1930320146</t>
+          <t>12977695</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930320146</t>
+          <t>https://m.place.naver.com/place/12977695</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>베럴짐 헬스앤피티 여의도점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bettergym_yeouido@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1488-2024</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 영등포구 국제금융로 78 11층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bettergym_yeouido</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>942</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1024</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1912472666</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1912472666</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 대림역점</t>
+          <t>바디채널 바레톤 여의도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym22@naver.com</t>
+          <t>bodych16@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1393-4002</t>
+          <t>0507-1367-5553</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 도림로 135 건설스마트빌딩 지하2층</t>
+          <t>서울특별시 영등포구 여의대방로65길 24 호성빌딩 3, 4층 바디채널 바레톤 여의도점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym22/223898097447</t>
+          <t>https://www.bodychannel.co.kr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2821</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>884</v>
+        <v>1301</v>
       </c>
       <c r="R2" t="n">
-        <v>3705</v>
+        <v>1675</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,56 +636,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1283449838</t>
+          <t>1640622698</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283449838</t>
+          <t>https://m.place.naver.com/place/1640622698</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐베스트 당산생각공장점</t>
+          <t>바론짐 PT &amp; 필라테스 선유도점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gymbest2@naver.com</t>
+          <t>barongym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1449-4666</t>
+          <t>0507-1441-4014</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 영등포로 150 생각공장 당산 C동 지하1층 엘113, 122호</t>
+          <t>서울특별시 영등포구 양평로 127 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymbest2</t>
+          <t>https://litt.ly/barongym2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>967</v>
+        <v>119</v>
       </c>
       <c r="Q3" t="n">
-        <v>1261</v>
+        <v>1423</v>
       </c>
       <c r="R3" t="n">
-        <v>2228</v>
+        <v>1542</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2066500608</t>
+          <t>2019478029</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066500608</t>
+          <t>https://m.place.naver.com/place/2019478029</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바론짐 PT &amp; 필라테스 선유도점</t>
+          <t>오로짐 여성전용PT &amp; 헬스 &amp; 필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>barongym@naver.com</t>
+          <t>orogym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1441-4014</t>
+          <t>0507-1390-1934</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 양평로 127 6층</t>
+          <t>서울특별시 영등포구 당산로 222 당산디오빌 204호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/barongym2</t>
+          <t>https://www.instagram.com/orogym_official/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1297</v>
+        <v>290</v>
       </c>
       <c r="R4" t="n">
-        <v>1417</v>
+        <v>379</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2019478029</t>
+          <t>2023410781</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019478029</t>
+          <t>https://m.place.naver.com/place/2023410781</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>885</v>
+        <v>921</v>
       </c>
       <c r="R5" t="n">
-        <v>1013</v>
+        <v>1053</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT리프 당산점</t>
+          <t>좋은습관 PT STUDIO 신길</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pt_studio_leaf@naver.com</t>
+          <t>ahfflk776@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1418-8235</t>
+          <t>0507-1493-2138</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 당산로 233 5층</t>
+          <t>서울특별시 영등포구 경인로114가길 11-1 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pt_studio_leaf</t>
+          <t>https://www.instagram.com/goodhabit_official_/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>756</v>
       </c>
       <c r="Q6" t="n">
-        <v>326</v>
+        <v>138</v>
       </c>
       <c r="R6" t="n">
-        <v>361</v>
+        <v>894</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2042258974</t>
+          <t>1067087287</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042258974</t>
+          <t>https://m.place.naver.com/place/1067087287</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디채널 바레톤 여의도점</t>
+          <t>PT위고</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodych16@naver.com</t>
+          <t>ssmnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1367-5553</t>
+          <t>0507-1354-1329</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의대방로65길 24 호성빌딩 3, 4층 바디채널 바레톤 여의도점</t>
+          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.bodychannel.co.kr</t>
+          <t>https://ptwigo.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,22 +1082,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>372</v>
+        <v>110</v>
       </c>
       <c r="Q7" t="n">
-        <v>1292</v>
+        <v>111</v>
       </c>
       <c r="R7" t="n">
-        <v>1664</v>
+        <v>221</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1640622698</t>
+          <t>1197252250</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1640622698</t>
+          <t>https://m.place.naver.com/place/1197252250</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바르다짐 PT&amp;헬스 신길동점</t>
+          <t>테리온휘트니스 당산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>generaltrainer@naver.com</t>
+          <t>cieleun1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1463-1434</t>
+          <t>0507-1371-9006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 가마산로89길 5 2, 3층</t>
+          <t>서울특별시 영등포구 영신로 238 6,7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barda_gym</t>
+          <t>https://www.instagram.com/terionfit/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>196</v>
+        <v>860</v>
       </c>
       <c r="Q8" t="n">
-        <v>268</v>
+        <v>1158</v>
       </c>
       <c r="R8" t="n">
-        <v>464</v>
+        <v>2018</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,56 +1200,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1684620094</t>
+          <t>1234987622</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684620094</t>
+          <t>https://m.place.naver.com/place/1234987622</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT위고</t>
+          <t>글래드짐 여의도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ssmnc@naver.com</t>
+          <t>gladgym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1354-1329</t>
+          <t>0507-1419-5962</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
+          <t>서울특별시 영등포구 여의대방로 394 우정빌딩 3층 301, 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://ptwigo.com</t>
+          <t>https://blog.naver.com/gladgym1/224237173348</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1270,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>110</v>
+        <v>360</v>
       </c>
       <c r="Q9" t="n">
-        <v>111</v>
+        <v>302</v>
       </c>
       <c r="R9" t="n">
-        <v>221</v>
+        <v>662</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1197252250</t>
+          <t>38426331</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197252250</t>
+          <t>https://m.place.naver.com/place/38426331</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>테리온휘트니스 당산점</t>
+          <t>아메리카요가 여의도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cieleun1@naver.com</t>
+          <t>ayo-yeouido@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1371-9006</t>
+          <t>0507-1415-4549</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 영신로 238 6,7층</t>
+          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/terionfit/</t>
+          <t>https://blog.naver.com/ayo-yeouido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>864</v>
+        <v>316</v>
       </c>
       <c r="Q10" t="n">
-        <v>1084</v>
+        <v>1204</v>
       </c>
       <c r="R10" t="n">
-        <v>1948</v>
+        <v>1520</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1234987622</t>
+          <t>12977695</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234987622</t>
+          <t>https://m.place.naver.com/place/12977695</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아메리카요가 여의도점</t>
+          <t>벤골프앤피트니스 여의도본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ayo-yeouido@naver.com</t>
+          <t>bengolf81@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-4549</t>
+          <t>0507-1432-7870</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
+          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ayo-yeouido</t>
+          <t>https://www.instagram.com/bengolf_fitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>312</v>
+        <v>192</v>
       </c>
       <c r="Q11" t="n">
-        <v>1192</v>
+        <v>146</v>
       </c>
       <c r="R11" t="n">
-        <v>1504</v>
+        <v>338</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12977695</t>
+          <t>1930320146</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12977695</t>
+          <t>https://m.place.naver.com/place/1930320146</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
@@ -624,10 +624,10 @@
         <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="R2" t="n">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바론짐 PT &amp; 필라테스 선유도점</t>
+          <t>원더핏 ONE THE FIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>barongym@naver.com</t>
+          <t>onthefit1210@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1441-4014</t>
+          <t>0507-1489-1648</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 양평로 127 6층</t>
+          <t>서울특별시 영등포구 영중로 157-11 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://litt.ly/barongym2</t>
+          <t>https://blog.naver.com/onthefit1210</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>119</v>
+        <v>705</v>
       </c>
       <c r="Q3" t="n">
-        <v>1423</v>
+        <v>275</v>
       </c>
       <c r="R3" t="n">
-        <v>1542</v>
+        <v>980</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2019478029</t>
+          <t>1238830476</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019478029</t>
+          <t>https://m.place.naver.com/place/1238830476</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오로짐 여성전용PT &amp; 헬스 &amp; 필라테스</t>
+          <t>바론짐 PT &amp; 필라테스 선유도점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>orogym@naver.com</t>
+          <t>barongym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1390-1934</t>
+          <t>0507-1441-4014</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 당산로 222 당산디오빌 204호</t>
+          <t>서울특별시 영등포구 양평로 127 6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orogym_official/</t>
+          <t>https://litt.ly/barongym2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="Q4" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>379</v>
+        <v>117</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2023410781</t>
+          <t>2019478029</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023410781</t>
+          <t>https://m.place.naver.com/place/2019478029</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>더라인핏 PT&amp;필라테스 신길점</t>
+          <t>좋은습관 PT STUDIO 신길</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>thelinefitpt@naver.com</t>
+          <t>mmcjmm@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1427-4181</t>
+          <t>0507-1493-2138</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
+          <t>서울특별시 영등포구 경인로114가길 11-1 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thelinefitpt</t>
+          <t>https://www.instagram.com/goodhabit_official_/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>132</v>
+        <v>756</v>
       </c>
       <c r="Q5" t="n">
-        <v>921</v>
+        <v>139</v>
       </c>
       <c r="R5" t="n">
-        <v>1053</v>
+        <v>895</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1186860079</t>
+          <t>1067087287</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186860079</t>
+          <t>https://m.place.naver.com/place/1067087287</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 신길</t>
+          <t>오로짐 여성전용PT &amp; 헬스 &amp; 필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ahfflk776@naver.com</t>
+          <t>orogym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1493-2138</t>
+          <t>0507-1390-1934</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로114가길 11-1 2층</t>
+          <t>서울특별시 영등포구 당산로 222 당산디오빌 204호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodhabit_official_/</t>
+          <t>https://www.instagram.com/orogym_official/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>756</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="n">
-        <v>138</v>
+        <v>290</v>
       </c>
       <c r="R6" t="n">
-        <v>894</v>
+        <v>380</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1012,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1067087287</t>
+          <t>2023410781</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1067087287</t>
+          <t>https://m.place.naver.com/place/2023410781</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT위고</t>
+          <t>헬스보이짐 롯데마트 양평점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ssmnc@naver.com</t>
+          <t>healthboy00092@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1354-1329</t>
+          <t>0507-1417-5125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
+          <t>서울특별시 영등포구 선유로 138 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://ptwigo.com</t>
+          <t>https://blog.naver.com/healthboy00092</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q7" t="n">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1106,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1197252250</t>
+          <t>2082705376</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197252250</t>
+          <t>https://m.place.naver.com/place/2082705376</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>테리온휘트니스 당산점</t>
+          <t>PT위고</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cieleun1@naver.com</t>
+          <t>ssmnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-9006</t>
+          <t>0507-1354-1329</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 영신로 238 6,7층</t>
+          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/terionfit/</t>
+          <t>https://ptwigo.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>860</v>
+        <v>110</v>
       </c>
       <c r="Q8" t="n">
-        <v>1158</v>
+        <v>111</v>
       </c>
       <c r="R8" t="n">
-        <v>2018</v>
+        <v>221</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1234987622</t>
+          <t>1197252250</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234987622</t>
+          <t>https://m.place.naver.com/place/1197252250</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>글래드짐 여의도점</t>
+          <t>벤골프앤피트니스 여의도본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gladgym1@naver.com</t>
+          <t>bengolf81@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-5962</t>
+          <t>0507-1432-7870</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의대방로 394 우정빌딩 3층 301, 302호</t>
+          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladgym1/224237173348</t>
+          <t>https://www.instagram.com/bengolf_fitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>360</v>
+        <v>190</v>
       </c>
       <c r="Q9" t="n">
-        <v>302</v>
+        <v>146</v>
       </c>
       <c r="R9" t="n">
-        <v>662</v>
+        <v>336</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>38426331</t>
+          <t>1930320146</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38426331</t>
+          <t>https://m.place.naver.com/place/1930320146</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아메리카요가 여의도점</t>
+          <t>베럴짐 헬스앤피티 여의도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ayo-yeouido@naver.com</t>
+          <t>bettergym_yeouido@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1415-4549</t>
+          <t>0507-1488-2024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
+          <t>서울특별시 영등포구 국제금융로 78 11층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ayo-yeouido</t>
+          <t>https://blog.naver.com/bettergym_yeouido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="n">
-        <v>1204</v>
+        <v>945</v>
       </c>
       <c r="R10" t="n">
-        <v>1520</v>
+        <v>1029</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>12977695</t>
+          <t>1912472666</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12977695</t>
+          <t>https://m.place.naver.com/place/1912472666</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1410,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>벤골프앤피트니스 여의도본점</t>
+          <t>휘트니스피플 우먼 당산역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bengolf81@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1432-7870</t>
+          <t>02-2677-3912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
+          <t>서울특별시 영등포구 양평로 68 9층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengolf_fitness</t>
+          <t>https://fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>192</v>
+        <v>382</v>
       </c>
       <c r="Q11" t="n">
-        <v>146</v>
+        <v>1353</v>
       </c>
       <c r="R11" t="n">
-        <v>338</v>
+        <v>1735</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1930320146</t>
+          <t>1097419185</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930320146</t>
+          <t>https://m.place.naver.com/place/1097419185</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의대방로65길 24 호성빌딩 3, 4층 바디채널 바레톤 여의도점</t>
+          <t>서울 영등포구 여의대방로65길 24 호성빌딩 3, 4층 바디채널 바레톤 여의도점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o3j2</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 영중로 157-11 2층</t>
+          <t>서울 영등포구 영중로 157-11 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3ha26w</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 양평로 127 6층</t>
+          <t>서울 영등포구 양평로 127 6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w18ayig</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +824,10 @@
         <v>117</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="R4" t="n">
-        <v>117</v>
+        <v>1590</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로114가길 11-1 2층</t>
+          <t>서울 영등포구 경인로114가길 11-1 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdaimq4</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 당산로 222 당산디오빌 204호</t>
+          <t>서울 영등포구 당산로 222 당산디오빌 204호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxdymco</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1029,39 +1049,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 롯데마트 양평점</t>
+          <t>PT위고</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboy00092@naver.com</t>
+          <t>ssmnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-5125</t>
+          <t>0507-1354-1329</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 선유로 138 2층</t>
+          <t>서울 영등포구 경인로 874 세림빌딩 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy00092</t>
+          <t>https://ptwigo.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,13 +1096,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cyh2</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="R7" t="n">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2082705376</t>
+          <t>1197252250</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082705376</t>
+          <t>https://m.place.naver.com/place/1197252250</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT위고</t>
+          <t>벤골프앤피트니스 여의도본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ssmnc@naver.com</t>
+          <t>bengolf81@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1354-1329</t>
+          <t>0507-1432-7870</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
+          <t>서울 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://ptwigo.com</t>
+          <t>https://www.instagram.com/bengolf_fitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,33 +1189,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49s3a</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="Q8" t="n">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="R8" t="n">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1197252250</t>
+          <t>1930320146</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197252250</t>
+          <t>https://m.place.naver.com/place/1930320146</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>벤골프앤피트니스 여의도본점</t>
+          <t>베럴짐 헬스앤피티 여의도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bengolf81@naver.com</t>
+          <t>bettergym_yeouido@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1432-7870</t>
+          <t>0507-1488-2024</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
+          <t>서울 영등포구 국제금융로 78 11층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengolf_fitness</t>
+          <t>https://blog.naver.com/bettergym_yeouido</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wirpafn</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="n">
-        <v>146</v>
+        <v>945</v>
       </c>
       <c r="R9" t="n">
-        <v>336</v>
+        <v>1029</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1930320146</t>
+          <t>1912472666</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930320146</t>
+          <t>https://m.place.naver.com/place/1912472666</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,34 +1348,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>베럴짐 헬스앤피티 여의도점</t>
+          <t>휘트니스피플 우먼 당산역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bettergym_yeouido@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1488-2024</t>
+          <t>02-2677-3912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 국제금융로 78 11층</t>
+          <t>서울 영등포구 양평로 68 9층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym_yeouido</t>
+          <t>https://fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1358,10 +1394,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wrd4voz</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,17 +1409,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="Q10" t="n">
-        <v>945</v>
+        <v>1358</v>
       </c>
       <c r="R10" t="n">
-        <v>1029</v>
+        <v>1740</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1912472666</t>
+          <t>1097419185</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912472666</t>
+          <t>https://m.place.naver.com/place/1097419185</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1403,55 +1443,35 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>휘트니스피플 우먼 당산역점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>02-2677-3912</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 양평로 68 9층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://fitnesspeople.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,17 +1487,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1353</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1735</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,15 +1506,171 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1097419185</t>
+          <t>7470296</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097419185</t>
+          <t>https://m.place.naver.com/place/7470296</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>7343754</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7343754</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7368532</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7368532</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1000,10 +1000,10 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="R6" t="n">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 롯데마트 양평점</t>
+          <t>테리온휘트니스 당산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy00092@naver.com</t>
+          <t>cieleun1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-5125</t>
+          <t>0507-1371-9006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 선유로 138 2층</t>
+          <t>서울특별시 영등포구 영신로 238 6,7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy00092</t>
+          <t>https://www.instagram.com/terionfit/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>107</v>
+        <v>862</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>1191</v>
       </c>
       <c r="R8" t="n">
-        <v>132</v>
+        <v>2053</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2082705376</t>
+          <t>1234987622</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082705376</t>
+          <t>https://m.place.naver.com/place/1234987622</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,39 +1217,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT위고</t>
+          <t>벤골프앤피트니스 여의도본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ssmnc@naver.com</t>
+          <t>bengolf81@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1354-1329</t>
+          <t>0507-1432-7870</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
+          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://ptwigo.com</t>
+          <t>https://www.instagram.com/bengolf_fitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1270,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="Q9" t="n">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="R9" t="n">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1197252250</t>
+          <t>1930320146</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197252250</t>
+          <t>https://m.place.naver.com/place/1930320146</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>벤골프앤피트니스 여의도본점</t>
+          <t>베럴짐 헬스앤피티 여의도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bengolf81@naver.com</t>
+          <t>bettergym_yeouido@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-7870</t>
+          <t>0507-1488-2024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
+          <t>서울특별시 영등포구 국제금융로 78 11층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengolf_fitness</t>
+          <t>https://blog.naver.com/bettergym_yeouido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="Q10" t="n">
-        <v>146</v>
+        <v>945</v>
       </c>
       <c r="R10" t="n">
-        <v>336</v>
+        <v>1030</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1930320146</t>
+          <t>1912472666</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930320146</t>
+          <t>https://m.place.naver.com/place/1912472666</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,34 +1410,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베럴짐 헬스앤피티 여의도점</t>
+          <t>휘트니스피플 우먼 당산역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bettergym_yeouido@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1488-2024</t>
+          <t>02-2677-3912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 국제금융로 78 11층</t>
+          <t>서울특별시 영등포구 양평로 68 9층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym_yeouido</t>
+          <t>https://fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1463,17 +1467,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>85</v>
+        <v>382</v>
       </c>
       <c r="Q11" t="n">
-        <v>945</v>
+        <v>1364</v>
       </c>
       <c r="R11" t="n">
-        <v>1030</v>
+        <v>1746</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,113 +1486,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1912472666</t>
+          <t>1097419185</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912472666</t>
+          <t>https://m.place.naver.com/place/1097419185</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>휘트니스피플 우먼 당산역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>02-2677-3912</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 영등포구 양평로 68 9층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://fitnesspeople.co.kr/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1363</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1745</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1097419185</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1097419185</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐베스트 당산생각공장점</t>
+          <t>에이블짐 대림역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymbest2@naver.com</t>
+          <t>ablegym22@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1449-4666</t>
+          <t>0507-1393-4002</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 영등포로 150 생각공장 당산 C동 지하1층 엘113, 122호</t>
+          <t>서울특별시 영등포구 도림로 135 건설스마트빌딩 지하2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymbest2</t>
+          <t>https://blog.naver.com/ablegym22/223898097447</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1002</v>
+        <v>2844</v>
       </c>
       <c r="Q2" t="n">
-        <v>1267</v>
+        <v>956</v>
       </c>
       <c r="R2" t="n">
-        <v>2269</v>
+        <v>3800</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2066500608</t>
+          <t>1283449838</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066500608</t>
+          <t>https://m.place.naver.com/place/1283449838</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o3j2</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -774,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onthefit1210</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3ha26w</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +820,10 @@
         <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R4" t="n">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -868,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orogym_official/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxdymco</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w18ayig</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1039,7 +1055,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mmcjmm@naver.com</t>
+          <t>goodhabitshingil@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1056,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodhabit_official_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdaimq4</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1128,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>테리온휘트니스 당산점</t>
+          <t>글래드짐 여의도점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cieleun1@naver.com</t>
+          <t>gladgym1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-9006</t>
+          <t>0507-1419-5962</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 영신로 238 6,7층</t>
+          <t>서울특별시 영등포구 여의대방로 394 우정빌딩 3층 301, 302호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/terionfit/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44z3w</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>862</v>
+        <v>360</v>
       </c>
       <c r="Q8" t="n">
-        <v>1191</v>
+        <v>304</v>
       </c>
       <c r="R8" t="n">
-        <v>2053</v>
+        <v>664</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1234987622</t>
+          <t>38426331</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234987622</t>
+          <t>https://m.place.naver.com/place/38426331</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1244,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengolf_fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49s3a</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q9" t="n">
         <v>146</v>
       </c>
       <c r="R9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1338,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym_yeouido</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1376,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wirpafn</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1376,10 +1408,10 @@
         <v>85</v>
       </c>
       <c r="Q10" t="n">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="R10" t="n">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1405,61 +1437,61 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 당산역점</t>
+          <t>더라인핏 PT&amp;필라테스 신길점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
+          <t>thelinefitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-2677-3912</t>
+          <t>0507-1427-4181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 양평로 68 9층</t>
+          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://fitnesspeople.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v79r</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>382</v>
+        <v>133</v>
       </c>
       <c r="Q11" t="n">
-        <v>1364</v>
+        <v>929</v>
       </c>
       <c r="R11" t="n">
-        <v>1746</v>
+        <v>1062</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,15 +1518,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1097419185</t>
+          <t>1186860079</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097419185</t>
+          <t>https://m.place.naver.com/place/1186860079</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>영자피트니스 영등포 신풍역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yjfitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1351-4466</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 영등포구 신길로 39 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs0x7</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>892</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>979</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1871</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1532915086</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1532915086</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="Q2" t="n">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="R2" t="n">
-        <v>3800</v>
+        <v>3804</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o3j2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -778,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/onthefit1210</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3ha26w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -820,10 +812,10 @@
         <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R4" t="n">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -876,34 +868,30 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/orogym_official/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxdymco</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w18ayig</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1038,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1039,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goodhabitshingil@naver.com</t>
+          <t>mmcjmm@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1072,7 +1056,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/goodhabit_official_/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdaimq4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1136,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1150,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gladgym1/224237173348</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1160,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44z3w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1234,41 +1210,41 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>벤골프앤피트니스 여의도본점</t>
+          <t>아메리카요가 여의도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bengolf81@naver.com</t>
+          <t>ayo-yeouido@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1432-7870</t>
+          <t>0507-1415-4549</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
+          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ayo-yeouido</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,24 +1254,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49s3a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>191</v>
+        <v>318</v>
       </c>
       <c r="Q9" t="n">
-        <v>146</v>
+        <v>1208</v>
       </c>
       <c r="R9" t="n">
-        <v>337</v>
+        <v>1526</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1930320146</t>
+          <t>12977695</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930320146</t>
+          <t>https://m.place.naver.com/place/12977695</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>베럴짐 헬스앤피티 여의도점</t>
+          <t>더라인핏 PT&amp;필라테스 신길점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bettergym_yeouido@naver.com</t>
+          <t>thelinefitpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1488-2024</t>
+          <t>0507-1427-4181</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 국제금융로 78 11층</t>
+          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/thelinefitpt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,24 +1348,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wirpafn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="Q10" t="n">
-        <v>947</v>
+        <v>929</v>
       </c>
       <c r="R10" t="n">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1912472666</t>
+          <t>1186860079</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912472666</t>
+          <t>https://m.place.naver.com/place/1186860079</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더라인핏 PT&amp;필라테스 신길점</t>
+          <t>베럴짐 헬스앤피티 여의도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>thelinefitpt@naver.com</t>
+          <t>bettergym_yeouido@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1427-4181</t>
+          <t>0507-1488-2024</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
+          <t>서울특별시 영등포구 국제금융로 78 11층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bettergym_yeouido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,24 +1442,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v79r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="Q11" t="n">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="R11" t="n">
-        <v>1062</v>
+        <v>1032</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,115 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1186860079</t>
+          <t>1912472666</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186860079</t>
+          <t>https://m.place.naver.com/place/1912472666</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>영자피트니스 영등포 신풍역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>yjfitness4@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1351-4466</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 영등포구 신길로 39 지하1층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs0x7</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>892</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>979</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1871</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1532915086</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1532915086</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="Q2" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="R2" t="n">
-        <v>3804</v>
+        <v>3811</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         <v>374</v>
       </c>
       <c r="Q3" t="n">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="R3" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R4" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1000,10 +1000,10 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>1499</v>
+        <v>1518</v>
       </c>
       <c r="R6" t="n">
-        <v>1616</v>
+        <v>1635</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 신길</t>
+          <t>위아핏 당산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mmcjmm@naver.com</t>
+          <t>dktjd303@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1493-2138</t>
+          <t>0507-1375-9366</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로114가길 11-1 2층</t>
+          <t>서울특별시 영등포구 국회대로29길 6 더 라임 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodhabit_official_/</t>
+          <t>https://blog.naver.com/dktjd303</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>756</v>
+        <v>230</v>
       </c>
       <c r="Q7" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="R7" t="n">
-        <v>895</v>
+        <v>383</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1067087287</t>
+          <t>1332672633</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1067087287</t>
+          <t>https://m.place.naver.com/place/1332672633</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1123,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>글래드짐 여의도점</t>
+          <t>PT위고</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gladgym1@naver.com</t>
+          <t>ssmnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1419-5962</t>
+          <t>0507-1354-1329</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의대방로 394 우정빌딩 3층 301, 302호</t>
+          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladgym1/224237173348</t>
+          <t>https://ptwigo.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="Q8" t="n">
-        <v>304</v>
+        <v>111</v>
       </c>
       <c r="R8" t="n">
-        <v>664</v>
+        <v>221</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38426331</t>
+          <t>1197252250</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38426331</t>
+          <t>https://m.place.naver.com/place/1197252250</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1311,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더라인핏 PT&amp;필라테스 신길점</t>
+          <t>벤골프앤피트니스 여의도본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>thelinefitpt@naver.com</t>
+          <t>bengolf81@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1427-4181</t>
+          <t>0507-1432-7870</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
+          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thelinefitpt</t>
+          <t>https://www.instagram.com/bengolf_fitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="Q10" t="n">
-        <v>929</v>
+        <v>147</v>
       </c>
       <c r="R10" t="n">
-        <v>1062</v>
+        <v>338</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1186860079</t>
+          <t>1930320146</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186860079</t>
+          <t>https://m.place.naver.com/place/1930320146</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베럴짐 헬스앤피티 여의도점</t>
+          <t>더라인핏 PT&amp;필라테스 신길점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bettergym_yeouido@naver.com</t>
+          <t>thelinefitpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1488-2024</t>
+          <t>0507-1427-4181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 국제금융로 78 11층</t>
+          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym_yeouido</t>
+          <t>https://blog.naver.com/thelinefitpt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="Q11" t="n">
-        <v>947</v>
+        <v>929</v>
       </c>
       <c r="R11" t="n">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1912472666</t>
+          <t>1186860079</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912472666</t>
+          <t>https://m.place.naver.com/place/1186860079</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/영등포_PT.xlsx
+++ b/naver-place-crawler/results_health/영등포_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="Q2" t="n">
         <v>964</v>
       </c>
       <c r="R2" t="n">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -812,10 +812,10 @@
         <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1000,10 +1000,10 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>1518</v>
+        <v>1530</v>
       </c>
       <c r="R6" t="n">
-        <v>1635</v>
+        <v>1647</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q7" t="n">
         <v>153</v>
       </c>
       <c r="R7" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,46 +1116,46 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT위고</t>
+          <t>헬스보이짐 롯데마트 양평점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ssmnc@naver.com</t>
+          <t>healthboy00092@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1354-1329</t>
+          <t>0507-1417-5125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
+          <t>서울특별시 영등포구 선유로 138 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://ptwigo.com</t>
+          <t>https://blog.naver.com/healthboy00092</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q8" t="n">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="R8" t="n">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,56 +1200,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1197252250</t>
+          <t>2082705376</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197252250</t>
+          <t>https://m.place.naver.com/place/2082705376</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아메리카요가 여의도점</t>
+          <t>PT위고</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ayo-yeouido@naver.com</t>
+          <t>ssmnc@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1415-4549</t>
+          <t>0507-1354-1329</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
+          <t>서울특별시 영등포구 경인로 874 세림빌딩 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ayo-yeouido</t>
+          <t>https://ptwigo.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1270,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>318</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="n">
-        <v>1208</v>
+        <v>111</v>
       </c>
       <c r="R9" t="n">
-        <v>1526</v>
+        <v>221</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12977695</t>
+          <t>1197252250</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12977695</t>
+          <t>https://m.place.naver.com/place/1197252250</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>벤골프앤피트니스 여의도본점</t>
+          <t>글래드짐 여의도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bengolf81@naver.com</t>
+          <t>gladgym1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-7870</t>
+          <t>0507-1419-5962</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 여의나루로 81 한마루빌딩 지하1층</t>
+          <t>서울특별시 영등포구 여의대방로 394 우정빌딩 3층 301, 302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengolf_fitness</t>
+          <t>https://blog.naver.com/gladgym1/224237173348</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>191</v>
+        <v>360</v>
       </c>
       <c r="Q10" t="n">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="R10" t="n">
-        <v>338</v>
+        <v>664</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1930320146</t>
+          <t>38426331</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930320146</t>
+          <t>https://m.place.naver.com/place/38426331</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더라인핏 PT&amp;필라테스 신길점</t>
+          <t>아메리카요가 여의도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>thelinefitpt@naver.com</t>
+          <t>ayo-yeouido@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1427-4181</t>
+          <t>0507-1415-4549</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 영등포구 가마산로 587 3층, 4층</t>
+          <t>서울 영등포구 여의대방로 394 우정빌딩 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thelinefitpt</t>
+          <t>https://blog.naver.com/ayo-yeouido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="Q11" t="n">
-        <v>929</v>
+        <v>1208</v>
       </c>
       <c r="R11" t="n">
-        <v>1062</v>
+        <v>1526</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1186860079</t>
+          <t>12977695</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186860079</t>
+          <t>https://m.place.naver.com/place/12977695</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
